--- a/Database/Financial_statment.xlsx
+++ b/Database/Financial_statment.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46123.63381944445</v>
+        <v>46123</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>15:12:42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Fund added to account</t>
+          <t>Credits Fund added to account</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -482,7 +482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-11 15:14:13.592150</t>
+          <t>2026-04-21 13:26:08.827049</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,92 +492,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stock is Bought ACC.NS with Quantity 10</t>
+          <t>Stock is Bought PNBHOUSING.NS with Quantity 10</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14250</v>
+        <v>9880</v>
       </c>
       <c r="F3" t="n">
-        <v>85750</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-11 15:14:13.592150</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stock is Bought ACC.NS with Quantity 10</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>14250</v>
-      </c>
-      <c r="F4" t="n">
-        <v>71500</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-11 15:14:13.592150</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Debit</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Stock is Bought ACC.NS with Quantity 10</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>14250</v>
-      </c>
-      <c r="F5" t="n">
-        <v>57250</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-11 15:14:13.592150</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Credits</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Stock is Selled ACC.NS with Quantity 10</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>14250</v>
-      </c>
-      <c r="F6" t="n">
-        <v>71500</v>
+        <v>90120</v>
       </c>
     </row>
   </sheetData>

--- a/Database/Financial_statment.xlsx
+++ b/Database/Financial_statment.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,16 +457,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="n">
-        <v>46123</v>
+        <v>46123.63381944445</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15:12:42</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Credits Fund added to account</t>
+          <t>Fund added to account</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -482,7 +482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-21 13:26:08.827049</t>
+          <t>2026-04-11 15:14:13.592150</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -492,14 +492,92 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Stock is Bought PNBHOUSING.NS with Quantity 10</t>
+          <t>Stock is Bought ACC.NS with Quantity 10</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>9880</v>
+        <v>14250</v>
       </c>
       <c r="F3" t="n">
-        <v>90120</v>
+        <v>85750</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-11 15:14:13.592150</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Stock is Bought ACC.NS with Quantity 10</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>14250</v>
+      </c>
+      <c r="F4" t="n">
+        <v>71500</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-11 15:14:13.592150</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Debit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stock is Bought ACC.NS with Quantity 10</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>14250</v>
+      </c>
+      <c r="F5" t="n">
+        <v>57250</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-11 15:14:13.592150</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Credits</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Stock is Selled ACC.NS with Quantity 10</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>14250</v>
+      </c>
+      <c r="F6" t="n">
+        <v>71500</v>
       </c>
     </row>
   </sheetData>
